--- a/mavenprojectSCR/ooxml-pie-chart.xlsx
+++ b/mavenprojectSCR/ooxml-pie-chart.xlsx
@@ -1,13 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr date1904="false"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10110"/>
+  <workbookPr defaultThemeVersion="202300"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/andrewhinton/Documents/GitHub/wizardfrontend/mavenprojectSCR/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02BAAEE6-AA5B-3349-9380-2B8B3937A9CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView activeTab="0"/>
+    <workbookView xWindow="0" yWindow="520" windowWidth="26240" windowHeight="15260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="piechart" r:id="rId3" sheetId="1"/>
+    <sheet name="piechart" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -26,13 +34,12 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color indexed="8"/>
-      <name val="Calibri"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -42,7 +49,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="darkGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
@@ -60,16 +67,33 @@
   <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="1"/>
+  <c:style val="2"/>
   <c:chart>
     <c:title>
       <c:tx>
         <c:rich>
-          <a:bodyPr anchor="t" rtlCol="false"/>
+          <a:bodyPr rtlCol="0" anchor="t"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr algn="l">
@@ -83,49 +107,90 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
-      <c:overlay val="false"/>
+      <c:overlay val="0"/>
     </c:title>
-    <c:autoTitleDeleted val="false"/>
+    <c:autoTitleDeleted val="0"/>
+    <c:view3D>
+      <c:rotX val="15"/>
+      <c:rotY val="0"/>
+      <c:rAngAx val="0"/>
+    </c:view3D>
+    <c:floor>
+      <c:thickness val="0"/>
+    </c:floor>
+    <c:sideWall>
+      <c:thickness val="0"/>
+    </c:sideWall>
+    <c:backWall>
+      <c:thickness val="0"/>
+    </c:backWall>
     <c:plotArea>
       <c:layout/>
       <c:pie3DChart>
-        <c:varyColors val="true"/>
+        <c:varyColors val="1"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:dPt>
             <c:idx val="0"/>
+            <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
                 <a:srgbClr val="7F7FFF"/>
               </a:solidFill>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-4179-A147-9A4C-7488EFFD389D}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="1"/>
+            <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
                 <a:srgbClr val="FF7F7F"/>
               </a:solidFill>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-4179-A147-9A4C-7488EFFD389D}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="2"/>
+            <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
                 <a:srgbClr val="7F7F7F"/>
               </a:solidFill>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-4179-A147-9A4C-7488EFFD389D}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dLbls>
-            <c:showLegendKey val="false"/>
-            <c:showVal val="false"/>
-            <c:showCatName val="false"/>
-            <c:showSerName val="false"/>
-            <c:showPercent val="true"/>
-            <c:showBubbleSize val="false"/>
-            <c:showLeaderLines val="false"/>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="1"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+            </c:extLst>
           </c:dLbls>
           <c:cat>
             <c:strRef>
@@ -148,27 +213,44 @@
             <c:numRef>
               <c:f>piechart!$A$2:$C$2</c:f>
               <c:numCache>
+                <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>5.0</c:v>
+                  <c:v>100</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>10.0</c:v>
+                  <c:v>10</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>34.0</c:v>
+                  <c:v>34</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000006-4179-A147-9A4C-7488EFFD389D}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="0"/>
+        </c:dLbls>
       </c:pie3DChart>
     </c:plotArea>
     <c:legend>
       <c:legendPos val="t"/>
-      <c:overlay val="false"/>
+      <c:overlay val="0"/>
     </c:legend>
-    <c:plotVisOnly val="true"/>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="zero"/>
+    <c:showDLblsOverMax val="1"/>
   </c:chart>
   <c:printSettings>
     <c:headerFooter/>
@@ -179,8 +261,8 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <xdr:twoCellAnchor editAs="twoCell">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
@@ -193,18 +275,24 @@
       <xdr:row>15</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
-    <xdr:graphicFrame>
+    <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="0" name="Diagramm0"/>
+        <xdr:cNvPr id="2" name="Diagramm0">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="0"/>
-        <a:ext cx="5867400" cy="2857500"/>
+        <a:ext cx="0" cy="0"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -213,35 +301,350 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="0E2841"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E8E8E8"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="156082"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="E97132"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="196B24"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="0F9ED5"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="A02B93"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="4EA72E"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="467886"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="96607D"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+    </a:ext>
+  </a:extLst>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="s" s="0">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s" s="0">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="n" s="0">
-        <v>5.0</v>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>100</v>
       </c>
-      <c r="B2" t="n" s="0">
-        <v>10.0</v>
+      <c r="B2">
+        <v>10</v>
       </c>
-      <c r="C2" t="n" s="0">
-        <v>34.0</v>
+      <c r="C2">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>